--- a/data/trans_orig/P33_MIN_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nº medio de minutos durante los cuales la población se echa la siesta</t>
+          <t>Nº medio de minutos durante los cuales la población se echa la siesta (tasa de respuesta: 37,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,4; 50,81</t>
+          <t>36,17; 51,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,74; 47,68</t>
+          <t>33,17; 46,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,5; 47,05</t>
+          <t>36,75; 46,81</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 37,55</t>
+          <t>6,98; 36,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,36; 48,47</t>
+          <t>38,76; 48,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 40,02</t>
+          <t>12,01; 40,21</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,44; 47,0</t>
+          <t>35,0; 46,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 33,44</t>
+          <t>5,13; 33,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 37,59</t>
+          <t>11,62; 37,53</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,8; 40,18</t>
+          <t>33,01; 40,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,98; 42,06</t>
+          <t>30,99; 41,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,17; 39,77</t>
+          <t>32,86; 39,35</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,8; 39,11</t>
+          <t>18,75; 39,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,02; 38,22</t>
+          <t>17,58; 38,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,82; 37,62</t>
+          <t>23,07; 38,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_MIN_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Habitat-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>42,57</t>
+          <t>42,86</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38,89</t>
+          <t>39,32</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40,99</t>
+          <t>41,34</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,17; 51,2</t>
+          <t>37,47; 51,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,17; 46,51</t>
+          <t>34,18; 47,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,75; 46,81</t>
+          <t>37,27; 46,89</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21,25</t>
+          <t>35,74</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43,25</t>
+          <t>44,35</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,58</t>
+          <t>39,69</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 36,96</t>
+          <t>31,9; 39,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,76; 48,17</t>
+          <t>40,63; 50,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 40,21</t>
+          <t>36,78; 42,77</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40,31</t>
+          <t>40,7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,81</t>
+          <t>30,96</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,58</t>
+          <t>36,11</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,0; 46,1</t>
+          <t>35,85; 46,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 33,74</t>
+          <t>26,75; 36,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 37,53</t>
+          <t>32,62; 39,68</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>36,55</t>
+          <t>36,59</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35,21</t>
+          <t>35,16</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35,91</t>
+          <t>35,9</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,01; 40,53</t>
+          <t>33,23; 40,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,99; 41,82</t>
+          <t>31,48; 41,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,86; 39,35</t>
+          <t>33,13; 39,05</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32,14</t>
+          <t>38,44</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,47</t>
+          <t>37,51</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31,83</t>
+          <t>38,01</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 39,01</t>
+          <t>36,09; 41,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 38,11</t>
+          <t>35,23; 40,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,07; 38,27</t>
+          <t>36,36; 39,82</t>
         </is>
       </c>
     </row>
